--- a/output/長岡赤十字病院_随意契約_X線関連.xlsx
+++ b/output/長岡赤十字病院_随意契約_X線関連.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -574,7 +574,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>デジタルX線ＴＶシステムAstorex i9の保守</t>
+          <t>X線透視診断装置 CUEVISTA保守</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr"/>
@@ -585,20 +585,20 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>令和6年4月1日</t>
+          <t>令和7年4月1日</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>クロスウィルメディカル株式会社新潟市東区紫竹卸新町1808-22</t>
+          <t>株式会社メディス長岡市旭岡1-19</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>3544200</v>
+        <v>1201200</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>https://www.nagaoka.jrc.or.jp/wp-content/uploads/2015/08/1a92e5278a5a5b9893a68344b4c4af972.pdf</t>
+          <t>https://www.nagaoka.jrc.or.jp/wp-content/uploads/2015/08/df40832c0b5dc002cc0c7f398170061c.pdf</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -616,7 +616,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>バイプレーン心臓血管撮影装置 Artis zee BC 保守</t>
+          <t>デジタルX線ＴＶシステムAstorex i9の保守</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr"/>
@@ -627,25 +627,25 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>令和7年4月1日</t>
+          <t>令和6年4月1日</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>株式会社メディス長岡市旭岡1-19</t>
+          <t>クロスウィルメディカル株式会社新潟市東区紫竹卸新町1808-22</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>18367800</v>
+        <v>3544200</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>https://www.nagaoka.jrc.or.jp/wp-content/uploads/2015/08/df40832c0b5dc002cc0c7f398170061c.pdf</t>
+          <t>https://www.nagaoka.jrc.or.jp/wp-content/uploads/2015/08/1a92e5278a5a5b9893a68344b4c4af972.pdf</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>血管撮影（CVS、アンギオ）</t>
+          <t>透視撮影台（X線テレビ）</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -658,7 +658,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>富士コンピューテッドラジオグラフィシステム（FCR）総合保守</t>
+          <t>バイプレーン心臓血管撮影装置 Artis zee BC 保守</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr"/>
@@ -669,25 +669,25 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>令和5年4月1日</t>
+          <t>令和7年4月1日</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>富士フイルムメディカル株式会社新潟市中央区白山浦2-1-1</t>
+          <t>株式会社メディス長岡市旭岡1-19</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2665740</v>
+        <v>18367800</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>https://www.nagaoka.jrc.or.jp/wp-content/uploads/2015/08/ad144dd9128402bc74628141a8d9e94f.pdf</t>
+          <t>https://www.nagaoka.jrc.or.jp/wp-content/uploads/2015/08/df40832c0b5dc002cc0c7f398170061c.pdf</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>一般撮影（レントゲン）</t>
+          <t>血管撮影（CVS、アンギオ）</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -700,7 +700,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>一般X線撮影装置の保守</t>
+          <t>富士コンピューテッドラジオグラフィシステム（FCR）総合保守</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr"/>
@@ -711,20 +711,20 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>令和6年4月1日</t>
+          <t>令和5年4月1日</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>クロスウィルメディカル株式会社新潟市東区紫竹卸新町1808-22</t>
+          <t>富士フイルムメディカル株式会社新潟市中央区白山浦2-1-1</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1899480</v>
+        <v>2665740</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>https://www.nagaoka.jrc.or.jp/wp-content/uploads/2015/08/1a92e5278a5a5b9893a68344b4c4af972.pdf</t>
+          <t>https://www.nagaoka.jrc.or.jp/wp-content/uploads/2015/08/ad144dd9128402bc74628141a8d9e94f.pdf</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -742,7 +742,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>富士コンピューテッドラジオグラフィシステム（FCR）総合保守</t>
+          <t>一般X線撮影装置の保守</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr"/>
@@ -753,20 +753,20 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>令和7年4月1日</t>
+          <t>令和6年4月1日</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>富士フイルムメディカル株式会社新潟市中央区白山浦2-1-1</t>
+          <t>クロスウィルメディカル株式会社新潟市東区紫竹卸新町1808-22</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1768140</v>
+        <v>1899480</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>https://www.nagaoka.jrc.or.jp/wp-content/uploads/2015/08/df40832c0b5dc002cc0c7f398170061c.pdf</t>
+          <t>https://www.nagaoka.jrc.or.jp/wp-content/uploads/2015/08/1a92e5278a5a5b9893a68344b4c4af972.pdf</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>令和6年4月1日</t>
+          <t>令和7年4月1日</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>https://www.nagaoka.jrc.or.jp/wp-content/uploads/2015/08/1a92e5278a5a5b9893a68344b4c4af972.pdf</t>
+          <t>https://www.nagaoka.jrc.or.jp/wp-content/uploads/2015/08/df40832c0b5dc002cc0c7f398170061c.pdf</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -826,7 +826,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>小児救急撮影室X線撮影装置の管球交換修理</t>
+          <t>富士コンピューテッドラジオグラフィシステム（FCR）総合保守</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr"/>
@@ -837,33 +837,75 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
+          <t>令和6年4月1日</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>富士フイルムメディカル株式会社新潟市中央区白山浦2-1-1</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>1768140</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nagaoka.jrc.or.jp/wp-content/uploads/2015/08/1a92e5278a5a5b9893a68344b4c4af972.pdf</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>一般撮影（レントゲン）</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>保守</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>小児救急撮影室X線撮影装置の管球交換修理</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>管財課新潟県長岡市千秋2丁目297番地1</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
           <t>令和5年4月21日</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>丸文通商株式会社石川県金沢市松島1丁目40</t>
         </is>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F12" s="4" t="n">
         <v>3942400</v>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>https://www.nagaoka.jrc.or.jp/wp-content/uploads/2015/08/ad144dd9128402bc74628141a8d9e94f.pdf</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>一般撮影（レントゲン）</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>保守</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -926,7 +968,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
     </row>
